--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484568_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484568_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4344</v>
+        <v>4.2948</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0686</v>
+        <v>4.7556</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6342</v>
+        <v>-0.4608</v>
       </c>
       <c r="G2" t="n">
         <v>3.7774</v>
@@ -610,13 +610,13 @@
         <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5812</v>
+        <v>0.2792</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.0837</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1895</v>
+        <v>0.3629</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3115</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1285</v>
+        <v>1.3074</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0817</v>
+        <v>2.2854</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9532</v>
+        <v>-0.978</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7408</v>
@@ -766,13 +766,13 @@
         <v>2.5656</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8877</v>
+        <v>1.0666</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6833</v>
+        <v>0.8869</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2044</v>
+        <v>0.1797</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3011</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3772</v>
+        <v>1.1709</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7085</v>
+        <v>-0.8283</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6687</v>
+        <v>1.9992</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.5891</v>
+        <v>-2.4207</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2365</v>
+        <v>-0.7891</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3527</v>
+        <v>-1.6317</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9801</v>
+        <v>-0.1857</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.4456</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.673</v>
+        <v>-1.6314</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6091</v>
+        <v>-2.235</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9294</v>
+        <v>-2.2347</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3204</v>
+        <v>-0.0003</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4661</v>
+        <v>2.7489</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0995</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5656</v>
+        <v>3.8484</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2333</v>
+        <v>0.8428</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2542</v>
+        <v>0.135</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9791</v>
+        <v>0.7077</v>
       </c>
       <c r="V5" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5339</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7049</v>
+        <v>1.1241</v>
       </c>
       <c r="E6" t="n">
-        <v>0.483</v>
+        <v>0.7775</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2219</v>
+        <v>0.3466</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0173</v>
+        <v>-2.5891</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.13</v>
+        <v>-1.2365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1473</v>
+        <v>-1.3527</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6127</v>
+        <v>-0.9801</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5294</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0833</v>
+        <v>-1.673</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5955</v>
+        <v>-1.6091</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6594</v>
+        <v>-1.9294</v>
       </c>
       <c r="O6" t="n">
-        <v>0.064</v>
+        <v>0.3204</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>0.91</v>
+        <v>0.9802</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7866</v>
+        <v>0.3232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1234</v>
+        <v>0.657</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9554</v>
+        <v>1.267</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5664</v>
+        <v>0.3535</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6805</v>
+        <v>0.0573</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2469</v>
+        <v>0.2962</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4207</v>
+        <v>0.0173</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7891</v>
+        <v>-0.13</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6317</v>
+        <v>0.1473</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1857</v>
+        <v>0.6127</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4456</v>
+        <v>0.5294</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.6314</v>
+        <v>0.0833</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.235</v>
+        <v>-0.5955</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.2347</v>
+        <v>-0.6594</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0003</v>
+        <v>0.064</v>
       </c>
       <c r="P7" t="n">
-        <v>2.7489</v>
+        <v>0.733</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8484</v>
+        <v>1.6493</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2383</v>
+        <v>0.5586</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7171999999999999</v>
+        <v>0.3609</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9555</v>
+        <v>0.1978</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2613</v>
+        <v>0.0518</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7796</v>
+        <v>-0.0027</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5183</v>
+        <v>0.0546</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0218</v>
+        <v>0.2526</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2303</v>
+        <v>1.0348</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2086</v>
+        <v>-0.7823</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5957</v>
+        <v>1.6097</v>
       </c>
       <c r="K8" t="n">
-        <v>2.195</v>
+        <v>2.1674</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5994</v>
+        <v>-0.5577</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5739</v>
+        <v>-1.3572</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9647</v>
+        <v>-1.1326</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6092</v>
+        <v>-0.2246</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0995</v>
+        <v>-2.0158</v>
       </c>
       <c r="R8" t="n">
         <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6348</v>
+        <v>0.1554</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6395</v>
+        <v>0.3929</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0048</v>
+        <v>-0.2376</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.945</v>
+        <v>0.0104</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6439</v>
+        <v>0.0104</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2506</v>
+        <v>-0.2685</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3052</v>
+        <v>1.1755</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0546</v>
+        <v>-1.444</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2526</v>
+        <v>0.0218</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0348</v>
+        <v>1.2303</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7823</v>
+        <v>-1.2086</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6097</v>
+        <v>1.5957</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1674</v>
+        <v>2.195</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5577</v>
+        <v>-0.5994</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3572</v>
+        <v>-1.5739</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1326</v>
+        <v>-0.9647</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2246</v>
+        <v>-0.6092</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="R9" t="n">
         <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1471</v>
+        <v>0.105</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0905</v>
+        <v>0.0355</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2376</v>
+        <v>0.0696</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0104</v>
+        <v>-0.945</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0104</v>
+        <v>0.6439</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7399</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3051</v>
+        <v>-0.1128</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4348</v>
+        <v>-0.5339</v>
       </c>
       <c r="G10" t="n">
         <v>-0.839</v>
@@ -1234,13 +1234,13 @@
         <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0842</v>
+        <v>0.0091</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1652</v>
+        <v>0.0272</v>
       </c>
       <c r="U10" t="n">
-        <v>0.081</v>
+        <v>-0.0181</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6512</v>
+        <v>-1.2992</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1951</v>
+        <v>0.4975</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8463</v>
+        <v>-1.7967</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0033</v>
@@ -1312,13 +1312,13 @@
         <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4255</v>
+        <v>-0.0735</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5324</v>
+        <v>-0.23</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1069</v>
+        <v>0.1565</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5889</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8127</v>
+        <v>-1.6935</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2345</v>
+        <v>-0.4374</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5782</v>
+        <v>-1.2561</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2197</v>
@@ -1390,13 +1390,13 @@
         <v>3.6651</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4648</v>
+        <v>0.6544</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.552</v>
+        <v>0.2451</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0872</v>
+        <v>0.4093</v>
       </c>
       <c r="V12" t="n">
         <v>-0.945</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.243900000000002</v>
+        <v>6.620200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>9.0168</v>
+        <v>10.3932</v>
       </c>
       <c r="F13" t="n">
         <v>-3.7729</v>
@@ -1435,7 +1435,7 @@
         <v>-1.5179</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.960900000000001</v>
+        <v>-2.9609</v>
       </c>
       <c r="I13" t="n">
         <v>1.4424</v>
@@ -1459,7 +1459,7 @@
         <v>-2.2458</v>
       </c>
       <c r="P13" t="n">
-        <v>7.3304</v>
+        <v>7.330400000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.7441</v>
@@ -1468,13 +1468,13 @@
         <v>21.0745</v>
       </c>
       <c r="S13" t="n">
-        <v>3.201300000000001</v>
+        <v>4.5778</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7165999999999997</v>
+        <v>2.093</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4846</v>
+        <v>2.4848</v>
       </c>
       <c r="V13" t="n">
         <v>-3.7695</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0584</v>
+        <v>2.152</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8487</v>
+        <v>1.6564</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2097</v>
+        <v>0.4956</v>
       </c>
       <c r="G14" t="n">
         <v>0.5694</v>
@@ -1546,13 +1546,13 @@
         <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8713</v>
+        <v>-0.0351</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.405</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2763</v>
+        <v>0.5622</v>
       </c>
       <c r="V14" t="n">
         <v>2.5339</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5829</v>
+        <v>1.6631</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8038</v>
+        <v>0.6115</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7791</v>
+        <v>1.0516</v>
       </c>
       <c r="G15" t="n">
         <v>1.0589</v>
@@ -1624,13 +1624,13 @@
         <v>1.0995</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3319</v>
+        <v>-0.2517</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1456</v>
+        <v>-0.0467</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4775</v>
+        <v>-0.205</v>
       </c>
       <c r="V15" t="n">
         <v>1.5889</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9415</v>
+        <v>1.141</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8003</v>
+        <v>2.8965</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8588</v>
+        <v>-1.7554</v>
       </c>
       <c r="G16" t="n">
         <v>3.1118</v>
@@ -1702,13 +1702,13 @@
         <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4955</v>
+        <v>-0.3993</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3084</v>
+        <v>-0.205</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6335</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2055</v>
+        <v>0.4691</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1988</v>
+        <v>0.4872</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0067</v>
+        <v>-0.0181</v>
       </c>
       <c r="G17" t="n">
         <v>0.6586</v>
@@ -1780,13 +1780,13 @@
         <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2541</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4404</v>
+        <v>-0.152</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1863</v>
+        <v>0.1616</v>
       </c>
       <c r="V17" t="n">
         <v>1.267</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3125</v>
+        <v>0.3694</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5094</v>
+        <v>1.894</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.822</v>
+        <v>-1.5247</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1993</v>
@@ -1858,13 +1858,13 @@
         <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0296</v>
+        <v>-0.3477</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4955</v>
+        <v>-0.1108</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5341</v>
+        <v>-0.2368</v>
       </c>
       <c r="V18" t="n">
         <v>0.6335</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7199</v>
+        <v>-0.7628</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.011</v>
+        <v>0.1177</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.709</v>
+        <v>-0.8806</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6217</v>
+        <v>1.3777</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0037</v>
+        <v>0.576</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6254</v>
+        <v>0.8017</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4468</v>
+        <v>3.5133</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2384</v>
+        <v>2.1024</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2084</v>
+        <v>1.4109</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0685</v>
+        <v>-2.1356</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.2347</v>
+        <v>-1.5264</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8338</v>
+        <v>-0.6092</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3665</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7489</v>
+        <v>-3.6651</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3823</v>
+        <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6111</v>
+        <v>0.2523</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2911</v>
+        <v>0.2696</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3199</v>
+        <v>-0.0174</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3428</v>
+        <v>-0.0104</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3428</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8649</v>
+        <v>-1.3946</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2139</v>
+        <v>-0.4918</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0788</v>
+        <v>-0.9028</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3777</v>
+        <v>-0.6217</v>
       </c>
       <c r="H20" t="n">
-        <v>0.576</v>
+        <v>0.0037</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8017</v>
+        <v>-0.6254</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5133</v>
+        <v>2.4468</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1024</v>
+        <v>2.2384</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4109</v>
+        <v>0.2084</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1356</v>
+        <v>-3.0685</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5264</v>
+        <v>-2.2347</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6092</v>
+        <v>-0.8338</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.3823</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6651</v>
+        <v>-2.7489</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2828</v>
+        <v>2.3823</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1502</v>
+        <v>-0.0635</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3658</v>
+        <v>-0.1896</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2155</v>
+        <v>0.1261</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.0104</v>
+        <v>-0.3428</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.0104</v>
+        <v>-0.3428</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5152</v>
+        <v>-1.8785</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2616</v>
+        <v>-0.877</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2536</v>
+        <v>-1.0015</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2894</v>
@@ -2092,13 +2092,13 @@
         <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4378</v>
+        <v>-0.8011</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.101</v>
+        <v>-0.7164</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3368</v>
+        <v>-0.0847</v>
       </c>
       <c r="V21" t="n">
         <v>2.212</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0222</v>
+        <v>-2.8765</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6988</v>
+        <v>-2.6027</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3234</v>
+        <v>-0.2738</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1208</v>
@@ -2170,13 +2170,13 @@
         <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1683</v>
+        <v>-0.0226</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3303</v>
+        <v>-0.2342</v>
       </c>
       <c r="U22" t="n">
-        <v>0.162</v>
+        <v>0.2115</v>
       </c>
       <c r="V22" t="n">
         <v>-1.267</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5974</v>
+        <v>-3.4851</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3694</v>
+        <v>0.0809</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9668</v>
+        <v>-3.5661</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0271</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8085</v>
+        <v>-0.6963</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0196</v>
+        <v>-0.3081</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7889</v>
+        <v>-0.3882</v>
       </c>
       <c r="V23" t="n">
         <v>-2.212</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2438</v>
+        <v>-4.6029</v>
       </c>
       <c r="E24" t="n">
-        <v>3.772900000000001</v>
+        <v>3.7727</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.016900000000001</v>
+        <v>-8.3758</v>
       </c>
       <c r="G24" t="n">
         <v>1.5181</v>
       </c>
       <c r="H24" t="n">
-        <v>2.960700000000001</v>
+        <v>2.9607</v>
       </c>
       <c r="I24" t="n">
         <v>-1.4427</v>
@@ -2314,7 +2314,7 @@
         <v>-10.3802</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.688600000000001</v>
+        <v>-3.6886</v>
       </c>
       <c r="P24" t="n">
         <v>-7.3303</v>
@@ -2326,13 +2326,13 @@
         <v>13.7442</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.2015</v>
+        <v>-2.5604</v>
       </c>
       <c r="T24" t="n">
         <v>-2.4848</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7167</v>
+        <v>-0.07569999999999988</v>
       </c>
       <c r="V24" t="n">
         <v>3.7696</v>
